--- a/inst/extdata/pvdat.xlsx
+++ b/inst/extdata/pvdat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10314"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krazy\Documents\pvest\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mr.bean/Documents/Research_UCLA/Packages/pvest/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E47618D-921D-455E-9F30-CC149C4AE247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F11866-710A-CE46-9406-4BC066A6E62B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="2085" windowWidth="21600" windowHeight="11835" xr2:uid="{13E884F8-8516-40EF-9BB8-FD1504D05D75}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{13E884F8-8516-40EF-9BB8-FD1504D05D75}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="183">
   <si>
     <t>species</t>
   </si>
@@ -177,21 +175,6 @@
   </si>
   <si>
     <t>ANGE</t>
-  </si>
-  <si>
-    <t>H20_533_2</t>
-  </si>
-  <si>
-    <t>H20_533_1</t>
-  </si>
-  <si>
-    <t>H21_39_3</t>
-  </si>
-  <si>
-    <t>H20_350_1</t>
-  </si>
-  <si>
-    <t>H20_350_2</t>
   </si>
   <si>
     <t>Arctostaphylos bakeri</t>
@@ -1103,9 +1086,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41860F56-5001-4285-B0BB-E6AF41ACC529}">
   <dimension ref="A1:S295"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,7 +1145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1207,7 +1190,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -1267,7 +1250,7 @@
         <v>0.39233279827127288</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
@@ -1327,7 +1310,7 @@
         <v>0.34237905349528819</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -1387,7 +1370,7 @@
         <v>0.30566750936752601</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -1447,7 +1430,7 @@
         <v>0.30823889193011977</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -1507,7 +1490,7 @@
         <v>0.13615870728981319</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
@@ -1567,7 +1550,7 @@
         <v>0.2096111512123956</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -1627,7 +1610,7 @@
         <v>0.22600905124504231</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
@@ -1687,7 +1670,7 @@
         <v>0.2096111512123956</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
@@ -1747,7 +1730,7 @@
         <v>0.25472415628102008</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
@@ -1807,7 +1790,7 @@
         <v>0.23712481846429104</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
@@ -1867,7 +1850,7 @@
         <v>0.26274332929127003</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
@@ -1927,7 +1910,7 @@
         <v>0.26893930331878307</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>32</v>
       </c>
@@ -1987,7 +1970,7 @@
         <v>0.19807713315401448</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -2047,7 +2030,7 @@
         <v>0.34814690828581019</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
@@ -2107,7 +2090,7 @@
         <v>0.28067286063694941</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>32</v>
       </c>
@@ -2167,7 +2150,7 @@
         <v>0.48701944556670712</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -2227,7 +2210,7 @@
         <v>0.22084912810232901</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>35</v>
       </c>
@@ -2243,12 +2226,12 @@
       <c r="E20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>39</v>
+      <c r="F20" s="5">
+        <v>1</v>
       </c>
       <c r="G20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANGEH20_533_2</v>
+        <v>ANGE1</v>
       </c>
       <c r="H20" s="6">
         <v>1.4322206894445288</v>
@@ -2287,7 +2270,7 @@
         <v>0.14070344032275703</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>35</v>
       </c>
@@ -2303,12 +2286,12 @@
       <c r="E21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>40</v>
+      <c r="F21" s="5">
+        <v>2</v>
       </c>
       <c r="G21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANGEH20_533_1</v>
+        <v>ANGE2</v>
       </c>
       <c r="H21" s="6">
         <v>1.488460805624499</v>
@@ -2347,7 +2330,7 @@
         <v>0.21310092913933718</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
@@ -2363,12 +2346,12 @@
       <c r="E22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>41</v>
+      <c r="F22" s="5">
+        <v>3</v>
       </c>
       <c r="G22" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANGEH21_39_3</v>
+        <v>ANGE3</v>
       </c>
       <c r="H22" s="6">
         <v>1.2276186035264043</v>
@@ -2407,7 +2390,7 @@
         <v>0.17322882585430713</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -2423,12 +2406,12 @@
       <c r="E23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>42</v>
+      <c r="F23" s="5">
+        <v>4</v>
       </c>
       <c r="G23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANGEH20_350_1</v>
+        <v>ANGE4</v>
       </c>
       <c r="H23" s="6">
         <v>1.5371152919298154</v>
@@ -2467,7 +2450,7 @@
         <v>0.30108890101863289</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
@@ -2483,12 +2466,12 @@
       <c r="E24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>43</v>
+      <c r="F24" s="5">
+        <v>5</v>
       </c>
       <c r="G24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>ANGEH20_350_2</v>
+        <v>ANGE5</v>
       </c>
       <c r="H24" s="6">
         <v>1.5913228588466097</v>
@@ -2527,21 +2510,21 @@
         <v>0.31640072426329063</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F25" s="5">
         <v>1</v>
@@ -2587,21 +2570,21 @@
         <v>0.23855356881955792</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F26" s="5">
         <v>2</v>
@@ -2647,21 +2630,21 @@
         <v>0.30365987044857262</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F27" s="5">
         <v>3</v>
@@ -2707,21 +2690,21 @@
         <v>0.2761197879016774</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F28" s="5">
         <v>4</v>
@@ -2767,21 +2750,21 @@
         <v>0.28353682823181658</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F29" s="5">
         <v>5</v>
@@ -2827,21 +2810,21 @@
         <v>0.28850855615373083</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F30" s="5">
         <v>6</v>
@@ -2887,12 +2870,12 @@
         <v>0.29795899027565576</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>29</v>
@@ -2901,14 +2884,14 @@
         <v>25</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F31" s="8">
-        <v>306018</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BACCRA306018</v>
+        <v>BACCRA1</v>
       </c>
       <c r="H31" s="12">
         <v>6.2853540069968084</v>
@@ -2947,12 +2930,12 @@
       </c>
       <c r="S31" s="9"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>29</v>
@@ -2961,14 +2944,14 @@
         <v>25</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F32" s="8">
-        <v>306018</v>
+        <v>2</v>
       </c>
       <c r="G32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BACCRA306018</v>
+        <v>BACCRA2</v>
       </c>
       <c r="H32" s="9">
         <v>3.3411409870014706</v>
@@ -3007,12 +2990,12 @@
       </c>
       <c r="S32" s="9"/>
     </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>29</v>
@@ -3021,14 +3004,14 @@
         <v>25</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F33" s="8">
-        <v>310035</v>
+        <v>3</v>
       </c>
       <c r="G33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BACCRA310035</v>
+        <v>BACCRA3</v>
       </c>
       <c r="H33" s="12">
         <v>3.2561070019105753</v>
@@ -3067,12 +3050,12 @@
       </c>
       <c r="S33" s="9"/>
     </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>29</v>
@@ -3081,14 +3064,14 @@
         <v>25</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F34" s="8">
-        <v>411167</v>
+        <v>4</v>
       </c>
       <c r="G34" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BACCRA411167</v>
+        <v>BACCRA4</v>
       </c>
       <c r="H34" s="9">
         <v>5.0117564491236619</v>
@@ -3127,12 +3110,12 @@
       </c>
       <c r="S34" s="9"/>
     </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>29</v>
@@ -3141,14 +3124,14 @@
         <v>25</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F35" s="8">
-        <v>715072</v>
+        <v>5</v>
       </c>
       <c r="G35" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>BACCRA715072</v>
+        <v>BACCRA5</v>
       </c>
       <c r="H35" s="9">
         <v>3.9435918684786984</v>
@@ -3187,12 +3170,12 @@
       </c>
       <c r="S35" s="9"/>
     </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>24</v>
@@ -3201,7 +3184,7 @@
         <v>30</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F36" s="8">
         <v>1</v>
@@ -3247,12 +3230,12 @@
         <v>0.47365490905290392</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>24</v>
@@ -3261,7 +3244,7 @@
         <v>30</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F37" s="8">
         <v>2</v>
@@ -3307,12 +3290,12 @@
         <v>0.3820038674050471</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>24</v>
@@ -3321,7 +3304,7 @@
         <v>30</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F38" s="8">
         <v>3</v>
@@ -3367,12 +3350,12 @@
         <v>0.34169729773124713</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>24</v>
@@ -3381,7 +3364,7 @@
         <v>30</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F39" s="8">
         <v>4</v>
@@ -3427,12 +3410,12 @@
         <v>0.34179696687569328</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>24</v>
@@ -3441,7 +3424,7 @@
         <v>30</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F40" s="8">
         <v>5</v>
@@ -3487,12 +3470,12 @@
         <v>0.32491825793497753</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>24</v>
@@ -3501,7 +3484,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F41" s="8">
         <v>6</v>
@@ -3547,9 +3530,9 @@
         <v>0.27081902204004288</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>33</v>
@@ -3561,7 +3544,7 @@
         <v>25</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F42" s="8">
         <v>1</v>
@@ -3607,9 +3590,9 @@
         <v>0.27239983554270292</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>33</v>
@@ -3621,7 +3604,7 @@
         <v>25</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F43" s="8">
         <v>2</v>
@@ -3667,9 +3650,9 @@
         <v>0.22400001844953632</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>33</v>
@@ -3681,7 +3664,7 @@
         <v>25</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F44" s="8">
         <v>3</v>
@@ -3727,9 +3710,9 @@
         <v>0.2307655022057262</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>33</v>
@@ -3741,7 +3724,7 @@
         <v>25</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F45" s="8">
         <v>4</v>
@@ -3787,9 +3770,9 @@
         <v>0.25201695816640124</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>33</v>
@@ -3801,7 +3784,7 @@
         <v>25</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F46" s="8">
         <v>5</v>
@@ -3847,12 +3830,12 @@
         <v>0.27083864134861724</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>29</v>
@@ -3861,7 +3844,7 @@
         <v>25</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F47" s="5">
         <v>1</v>
@@ -3907,12 +3890,12 @@
         <v>0.22764120650041192</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>29</v>
@@ -3921,7 +3904,7 @@
         <v>25</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F48" s="5">
         <v>3</v>
@@ -3967,12 +3950,12 @@
         <v>0.25141034811427143</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>29</v>
@@ -3981,7 +3964,7 @@
         <v>25</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F49" s="5">
         <v>4</v>
@@ -4027,12 +4010,12 @@
         <v>0.29669859156239281</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>29</v>
@@ -4041,7 +4024,7 @@
         <v>25</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F50" s="5">
         <v>5</v>
@@ -4087,12 +4070,12 @@
         <v>0.22224597984379282</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>29</v>
@@ -4101,7 +4084,7 @@
         <v>25</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F51" s="5">
         <v>6</v>
@@ -4147,12 +4130,12 @@
         <v>0.27069571147266597</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>24</v>
@@ -4161,7 +4144,7 @@
         <v>25</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F52" s="5">
         <v>1</v>
@@ -4207,12 +4190,12 @@
         <v>0.19911693276394204</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>24</v>
@@ -4221,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F53" s="5">
         <v>2</v>
@@ -4267,12 +4250,12 @@
         <v>0.2345990109624293</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>24</v>
@@ -4281,7 +4264,7 @@
         <v>25</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F54" s="5">
         <v>3</v>
@@ -4327,12 +4310,12 @@
         <v>0.28284185815664969</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>24</v>
@@ -4341,7 +4324,7 @@
         <v>25</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F55" s="5">
         <v>4</v>
@@ -4387,12 +4370,12 @@
         <v>0.2336823562221369</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>24</v>
@@ -4401,7 +4384,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F56" s="5">
         <v>6</v>
@@ -4447,21 +4430,21 @@
         <v>0.19998430176933796</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -4507,21 +4490,21 @@
         <v>0.1436431456041776</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F58" s="5">
         <v>2</v>
@@ -4567,21 +4550,21 @@
         <v>0.10375831416984724</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F59" s="5">
         <v>3</v>
@@ -4627,21 +4610,21 @@
         <v>0.14692363180646031</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F60" s="5">
         <v>5</v>
@@ -4687,21 +4670,21 @@
         <v>0.28371888826041702</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F61" s="5">
         <v>6</v>
@@ -4747,12 +4730,12 @@
         <v>0.21996757626572422</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>29</v>
@@ -4761,7 +4744,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F62" s="5">
         <v>4</v>
@@ -4807,12 +4790,12 @@
         <v>0.18127173051072534</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>29</v>
@@ -4821,7 +4804,7 @@
         <v>25</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F63" s="5">
         <v>8</v>
@@ -4867,12 +4850,12 @@
         <v>0.19605424994892315</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>29</v>
@@ -4881,7 +4864,7 @@
         <v>25</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F64" s="5">
         <v>9</v>
@@ -4927,12 +4910,12 @@
         <v>0.18255130250627985</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>29</v>
@@ -4941,7 +4924,7 @@
         <v>25</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F65" s="5">
         <v>2</v>
@@ -4987,12 +4970,12 @@
         <v>0.18618000977073598</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>29</v>
@@ -5001,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F66" s="5">
         <v>3</v>
@@ -5047,21 +5030,21 @@
         <v>0.22538800960224295</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F67" s="15">
         <v>1.1000000000000001</v>
@@ -5107,21 +5090,21 @@
         <v>0.43583293913268201</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F68" s="15">
         <v>1.2</v>
@@ -5167,21 +5150,21 @@
         <v>0.33554073425532815</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F69" s="15">
         <v>2</v>
@@ -5227,21 +5210,21 @@
         <v>0.30572976547418385</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F70" s="15">
         <v>2.1</v>
@@ -5287,21 +5270,21 @@
         <v>0.35275750500974096</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F71" s="15">
         <v>4</v>
@@ -5347,21 +5330,21 @@
         <v>0.31063559383250411</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F72" s="15">
         <v>4.0999999999999996</v>
@@ -5407,21 +5390,21 @@
         <v>0.36565846117321643</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -5467,21 +5450,21 @@
         <v>0.42892784784185634</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F74" s="5">
         <v>2</v>
@@ -5527,21 +5510,21 @@
         <v>0.40986907107510823</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F75" s="5">
         <v>3</v>
@@ -5587,21 +5570,21 @@
         <v>0.50545384550930572</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F76" s="5">
         <v>4</v>
@@ -5647,21 +5630,21 @@
         <v>0.38646559031644956</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F77" s="5">
         <v>5</v>
@@ -5707,21 +5690,21 @@
         <v>0.38007790817053699</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F78" s="5">
         <v>6</v>
@@ -5767,21 +5750,21 @@
         <v>0.37470774094502113</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F79" s="5">
         <v>1</v>
@@ -5827,21 +5810,21 @@
         <v>0.2373117842031294</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F80" s="5">
         <v>2</v>
@@ -5887,21 +5870,21 @@
         <v>0.29740897590445237</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F81" s="5">
         <v>3</v>
@@ -5947,21 +5930,21 @@
         <v>0.4332740618329623</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F82" s="5">
         <v>4</v>
@@ -6007,21 +5990,21 @@
         <v>0.25592382257697494</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F83" s="5">
         <v>5</v>
@@ -6067,21 +6050,21 @@
         <v>0.28289706640794715</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F84" s="5">
         <v>6</v>
@@ -6127,21 +6110,21 @@
         <v>0.3113073796867375</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F85" s="5">
         <v>1</v>
@@ -6187,21 +6170,21 @@
         <v>0.14877394046057499</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F86" s="5">
         <v>2</v>
@@ -6247,21 +6230,21 @@
         <v>8.4862938913817437E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F87" s="5">
         <v>3</v>
@@ -6307,21 +6290,21 @@
         <v>0.1021626018920932</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F88" s="5">
         <v>4</v>
@@ -6367,21 +6350,21 @@
         <v>7.7945286053388255E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F89" s="5">
         <v>5</v>
@@ -6427,21 +6410,21 @@
         <v>6.9628947467902866E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F90" s="5">
         <v>6</v>
@@ -6487,12 +6470,12 @@
         <v>9.52412716062674E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>29</v>
@@ -6501,7 +6484,7 @@
         <v>25</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F91" s="5">
         <v>1.1000000000000001</v>
@@ -6547,12 +6530,12 @@
         <v>0.12435504215764771</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>29</v>
@@ -6561,7 +6544,7 @@
         <v>25</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F92" s="5">
         <v>4.0999999999999996</v>
@@ -6607,12 +6590,12 @@
         <v>0.21319682001366519</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>29</v>
@@ -6621,7 +6604,7 @@
         <v>25</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F93" s="5">
         <v>5.0999999999999996</v>
@@ -6667,21 +6650,21 @@
         <v>0.18103274890261992</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F94" s="5">
         <v>1</v>
@@ -6727,21 +6710,21 @@
         <v>0.3701767240790062</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F95" s="5">
         <v>3</v>
@@ -6787,21 +6770,21 @@
         <v>0.43911940802728477</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F96" s="5">
         <v>4</v>
@@ -6847,21 +6830,21 @@
         <v>0.40886663313118227</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F97" s="5">
         <v>5</v>
@@ -6907,21 +6890,21 @@
         <v>0.37339531951659477</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F98" s="5">
         <v>6</v>
@@ -6967,21 +6950,21 @@
         <v>0.34938541155713621</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F99" s="5">
         <v>1</v>
@@ -7027,21 +7010,21 @@
         <v>0.40612261981039899</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F100" s="5">
         <v>2</v>
@@ -7087,21 +7070,21 @@
         <v>0.25566667662065662</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F101" s="5">
         <v>3</v>
@@ -7147,21 +7130,21 @@
         <v>0.26586405128540297</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F102" s="5">
         <v>4</v>
@@ -7207,21 +7190,21 @@
         <v>0.2496132899995791</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F103" s="5">
         <v>5</v>
@@ -7267,21 +7250,21 @@
         <v>0.28257131681110903</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F104" s="5">
         <v>6</v>
@@ -7327,21 +7310,21 @@
         <v>0.24549194845924904</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F105" s="5">
         <v>1</v>
@@ -7387,21 +7370,21 @@
         <v>0.38631626508546962</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F106" s="5">
         <v>2</v>
@@ -7447,21 +7430,21 @@
         <v>0.63632613196829779</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F107" s="5">
         <v>4</v>
@@ -7507,21 +7490,21 @@
         <v>0.52385716184789588</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F108" s="5">
         <v>5</v>
@@ -7567,21 +7550,21 @@
         <v>0.71555337714126244</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F109" s="5">
         <v>6</v>
@@ -7627,12 +7610,12 @@
         <v>0.40455146531368269</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>29</v>
@@ -7641,10 +7624,10 @@
         <v>37</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G110" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7687,12 +7670,12 @@
         <v>0.47910728644990164</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>29</v>
@@ -7701,10 +7684,10 @@
         <v>37</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G111" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7747,12 +7730,12 @@
         <v>0.44153158971042433</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>29</v>
@@ -7761,10 +7744,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G112" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7807,12 +7790,12 @@
         <v>0.37468509048396698</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>29</v>
@@ -7821,10 +7804,10 @@
         <v>37</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G113" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7867,12 +7850,12 @@
         <v>0.34029073708536373</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>29</v>
@@ -7881,10 +7864,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F114" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="G114" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7927,12 +7910,12 @@
         <v>0.47715450603065757</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>24</v>
@@ -7941,7 +7924,7 @@
         <v>25</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F115" s="5">
         <v>2</v>
@@ -7987,12 +7970,12 @@
         <v>0.25356374404251558</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>24</v>
@@ -8001,7 +7984,7 @@
         <v>25</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F116" s="5">
         <v>3</v>
@@ -8047,12 +8030,12 @@
         <v>0.28819748279252255</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>24</v>
@@ -8061,7 +8044,7 @@
         <v>25</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F117" s="5">
         <v>4</v>
@@ -8107,12 +8090,12 @@
         <v>0.26481941357866107</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>24</v>
@@ -8121,7 +8104,7 @@
         <v>25</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F118" s="5">
         <v>5</v>
@@ -8167,12 +8150,12 @@
         <v>0.27003786216181463</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>24</v>
@@ -8181,7 +8164,7 @@
         <v>25</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F119" s="5">
         <v>6</v>
@@ -8227,12 +8210,12 @@
         <v>0.26299767437131816</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>29</v>
@@ -8241,10 +8224,10 @@
         <v>37</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G120" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8287,12 +8270,12 @@
         <v>0.28032313209321602</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>29</v>
@@ -8301,10 +8284,10 @@
         <v>37</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G121" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8347,12 +8330,12 @@
         <v>0.29741041399541029</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>29</v>
@@ -8361,10 +8344,10 @@
         <v>37</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G122" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8407,12 +8390,12 @@
         <v>0.19581872667543629</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>29</v>
@@ -8421,10 +8404,10 @@
         <v>37</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G123" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8467,12 +8450,12 @@
         <v>0.26707724090641305</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>29</v>
@@ -8481,10 +8464,10 @@
         <v>37</v>
       </c>
       <c r="E124" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="G124" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8527,12 +8510,12 @@
         <v>0.26278664386550787</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>29</v>
@@ -8541,7 +8524,7 @@
         <v>25</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F125" s="5">
         <v>1</v>
@@ -8587,12 +8570,12 @@
         <v>0.19457245944112991</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>29</v>
@@ -8601,7 +8584,7 @@
         <v>25</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F126" s="5">
         <v>2</v>
@@ -8647,12 +8630,12 @@
         <v>0.22865645929347453</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>29</v>
@@ -8661,7 +8644,7 @@
         <v>25</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F127" s="5">
         <v>3</v>
@@ -8707,12 +8690,12 @@
         <v>0.19330780173819748</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>29</v>
@@ -8721,7 +8704,7 @@
         <v>25</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F128" s="5">
         <v>4</v>
@@ -8767,12 +8750,12 @@
         <v>0.22541104779491794</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>29</v>
@@ -8781,7 +8764,7 @@
         <v>25</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F129" s="5">
         <v>5</v>
@@ -8827,12 +8810,12 @@
         <v>0.27335174916945015</v>
       </c>
     </row>
-    <row r="130" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>29</v>
@@ -8841,7 +8824,7 @@
         <v>25</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F130" s="5">
         <v>6</v>
@@ -8887,21 +8870,21 @@
         <v>0.22635857562147876</v>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F131" s="5">
         <v>1</v>
@@ -8947,21 +8930,21 @@
         <v>0.4366659577124859</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F132" s="5">
         <v>2</v>
@@ -9007,21 +8990,21 @@
         <v>0.49364972134747687</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F133" s="5">
         <v>3</v>
@@ -9067,21 +9050,21 @@
         <v>0.53575926701651855</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F134" s="5">
         <v>5</v>
@@ -9127,21 +9110,21 @@
         <v>0.58508902387480088</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F135" s="5">
         <v>6</v>
@@ -9187,21 +9170,21 @@
         <v>0.97238322649855846</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F136" s="5">
         <v>1</v>
@@ -9247,21 +9230,21 @@
         <v>0.15481794645356606</v>
       </c>
     </row>
-    <row r="137" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F137" s="5">
         <v>2</v>
@@ -9307,21 +9290,21 @@
         <v>0.19437565062450338</v>
       </c>
     </row>
-    <row r="138" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F138" s="5">
         <v>3</v>
@@ -9367,21 +9350,21 @@
         <v>0.15795614742188535</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F139" s="5">
         <v>4</v>
@@ -9427,21 +9410,21 @@
         <v>0.18832772057534145</v>
       </c>
     </row>
-    <row r="140" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F140" s="5">
         <v>5</v>
@@ -9487,21 +9470,21 @@
         <v>0.18592021308017384</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F141" s="5">
         <v>6</v>
@@ -9547,12 +9530,12 @@
         <v>0.19324420563757189</v>
       </c>
     </row>
-    <row r="142" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>29</v>
@@ -9561,7 +9544,7 @@
         <v>25</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F142" s="8">
         <v>202030</v>
@@ -9607,12 +9590,12 @@
       </c>
       <c r="S142" s="9"/>
     </row>
-    <row r="143" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>29</v>
@@ -9621,7 +9604,7 @@
         <v>25</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F143" s="8">
         <v>511010</v>
@@ -9670,12 +9653,12 @@
         <v>-0.77312277019785114</v>
       </c>
     </row>
-    <row r="144" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>29</v>
@@ -9684,7 +9667,7 @@
         <v>25</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F144" s="8">
         <v>617080</v>
@@ -9730,12 +9713,12 @@
       </c>
       <c r="S144" s="9"/>
     </row>
-    <row r="145" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>29</v>
@@ -9744,7 +9727,7 @@
         <v>25</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F145" s="8">
         <v>921108</v>
@@ -9790,12 +9773,12 @@
       </c>
       <c r="S145" s="9"/>
     </row>
-    <row r="146" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>29</v>
@@ -9804,7 +9787,7 @@
         <v>25</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F146" s="8">
         <v>1021024</v>
@@ -9850,12 +9833,12 @@
       </c>
       <c r="S146" s="9"/>
     </row>
-    <row r="147" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>29</v>
@@ -9864,7 +9847,7 @@
         <v>25</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F147" s="8">
         <v>1124153</v>
@@ -9910,12 +9893,12 @@
       </c>
       <c r="S147" s="9"/>
     </row>
-    <row r="148" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>29</v>
@@ -9924,7 +9907,7 @@
         <v>37</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F148" s="5">
         <v>1</v>
@@ -9970,12 +9953,12 @@
         <v>0.50522001617762868</v>
       </c>
     </row>
-    <row r="149" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>29</v>
@@ -9984,7 +9967,7 @@
         <v>37</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F149" s="5">
         <v>2</v>
@@ -10030,12 +10013,12 @@
         <v>0.47506130825530257</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>29</v>
@@ -10044,7 +10027,7 @@
         <v>37</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F150" s="5">
         <v>3</v>
@@ -10090,12 +10073,12 @@
         <v>0.34452730741806903</v>
       </c>
     </row>
-    <row r="151" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>29</v>
@@ -10104,7 +10087,7 @@
         <v>37</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F151" s="5">
         <v>4</v>
@@ -10150,12 +10133,12 @@
         <v>0.4812541211907454</v>
       </c>
     </row>
-    <row r="152" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>29</v>
@@ -10164,7 +10147,7 @@
         <v>37</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F152" s="5">
         <v>5</v>
@@ -10210,12 +10193,12 @@
         <v>0.4690607327038358</v>
       </c>
     </row>
-    <row r="153" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>29</v>
@@ -10224,10 +10207,10 @@
         <v>37</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G153" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10270,12 +10253,12 @@
         <v>0.38420866089111977</v>
       </c>
     </row>
-    <row r="154" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>29</v>
@@ -10284,10 +10267,10 @@
         <v>37</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G154" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10330,12 +10313,12 @@
         <v>0.39734401308426326</v>
       </c>
     </row>
-    <row r="155" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>29</v>
@@ -10344,10 +10327,10 @@
         <v>37</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G155" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10390,12 +10373,12 @@
         <v>0.28967278491530529</v>
       </c>
     </row>
-    <row r="156" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B156" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>29</v>
@@ -10404,10 +10387,10 @@
         <v>37</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G156" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10450,12 +10433,12 @@
         <v>0.30222925986968263</v>
       </c>
     </row>
-    <row r="157" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>29</v>
@@ -10464,10 +10447,10 @@
         <v>37</v>
       </c>
       <c r="E157" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="G157" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10510,12 +10493,12 @@
         <v>0.3096662863720207</v>
       </c>
     </row>
-    <row r="158" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B158" s="18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>29</v>
@@ -10524,10 +10507,10 @@
         <v>37</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G158" s="5" t="str">
         <f t="shared" si="2"/>
@@ -10570,12 +10553,12 @@
         <v>0.3237765988167367</v>
       </c>
     </row>
-    <row r="159" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>29</v>
@@ -10584,7 +10567,7 @@
         <v>25</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F159" s="5">
         <v>1</v>
@@ -10630,12 +10613,12 @@
         <v>0.11788856853198129</v>
       </c>
     </row>
-    <row r="160" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>29</v>
@@ -10644,7 +10627,7 @@
         <v>25</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F160" s="5">
         <v>2</v>
@@ -10690,12 +10673,12 @@
         <v>0.2554282352617856</v>
       </c>
     </row>
-    <row r="161" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>29</v>
@@ -10704,7 +10687,7 @@
         <v>25</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F161" s="5">
         <v>3</v>
@@ -10750,12 +10733,12 @@
         <v>0.28943941005251206</v>
       </c>
     </row>
-    <row r="162" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>29</v>
@@ -10764,7 +10747,7 @@
         <v>25</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F162" s="5">
         <v>4</v>
@@ -10810,12 +10793,12 @@
         <v>0.28321933256431031</v>
       </c>
     </row>
-    <row r="163" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>29</v>
@@ -10824,7 +10807,7 @@
         <v>25</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F163" s="5">
         <v>5</v>
@@ -10870,12 +10853,12 @@
         <v>0.24127507500651554</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>29</v>
@@ -10884,7 +10867,7 @@
         <v>25</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F164" s="5">
         <v>6</v>
@@ -10930,21 +10913,21 @@
         <v>0.11714099157283024</v>
       </c>
     </row>
-    <row r="165" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F165" s="5">
         <v>1</v>
@@ -10990,21 +10973,21 @@
         <v>0.25151722299167795</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F166" s="5">
         <v>2</v>
@@ -11050,21 +11033,21 @@
         <v>0.16906615581794851</v>
       </c>
     </row>
-    <row r="167" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F167" s="5">
         <v>3</v>
@@ -11110,21 +11093,21 @@
         <v>0.19677431631106018</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F168" s="5">
         <v>4</v>
@@ -11170,21 +11153,21 @@
         <v>0.22884256090372745</v>
       </c>
     </row>
-    <row r="169" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F169" s="5">
         <v>5</v>
@@ -11230,21 +11213,21 @@
         <v>0.20211185194500986</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F170" s="5">
         <v>6</v>
@@ -11290,21 +11273,21 @@
         <v>0.14816557973205946</v>
       </c>
     </row>
-    <row r="171" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B171" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F171" s="5">
         <v>1</v>
@@ -11350,21 +11333,21 @@
         <v>0.37999947398444522</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F172" s="5">
         <v>3</v>
@@ -11410,21 +11393,21 @@
         <v>0.43060329597838864</v>
       </c>
     </row>
-    <row r="173" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F173" s="5">
         <v>4</v>
@@ -11470,21 +11453,21 @@
         <v>0.48151303433673548</v>
       </c>
     </row>
-    <row r="174" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F174" s="5">
         <v>5</v>
@@ -11530,21 +11513,21 @@
         <v>0.51667347296493671</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F175" s="5">
         <v>6</v>
@@ -11590,21 +11573,21 @@
         <v>0.51587179042929265</v>
       </c>
     </row>
-    <row r="176" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F176" s="17">
         <v>1</v>
@@ -11650,21 +11633,21 @@
         <v>0.4188435146473789</v>
       </c>
     </row>
-    <row r="177" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B177" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F177" s="17">
         <v>2</v>
@@ -11710,21 +11693,21 @@
         <v>0.34779864292915463</v>
       </c>
     </row>
-    <row r="178" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B178" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F178" s="17">
         <v>3</v>
@@ -11770,21 +11753,21 @@
         <v>0.51712541585616467</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F179" s="17">
         <v>4</v>
@@ -11830,21 +11813,21 @@
         <v>0.52524208873721068</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F180" s="17">
         <v>6</v>
@@ -11890,12 +11873,12 @@
         <v>0.40293532607621435</v>
       </c>
     </row>
-    <row r="181" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>24</v>
@@ -11904,7 +11887,7 @@
         <v>25</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F181" s="5">
         <v>1</v>
@@ -11950,12 +11933,12 @@
         <v>0.45723840860025888</v>
       </c>
     </row>
-    <row r="182" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>24</v>
@@ -11964,7 +11947,7 @@
         <v>25</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F182" s="5">
         <v>2</v>
@@ -12010,12 +11993,12 @@
         <v>0.47245458210074726</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>24</v>
@@ -12024,7 +12007,7 @@
         <v>25</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F183" s="5">
         <v>3</v>
@@ -12070,12 +12053,12 @@
         <v>0.52260766721920193</v>
       </c>
     </row>
-    <row r="184" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>24</v>
@@ -12084,7 +12067,7 @@
         <v>25</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F184" s="5">
         <v>4</v>
@@ -12130,12 +12113,12 @@
         <v>0.49776267137416452</v>
       </c>
     </row>
-    <row r="185" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>24</v>
@@ -12144,7 +12127,7 @@
         <v>25</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F185" s="5">
         <v>6</v>
@@ -12190,12 +12173,12 @@
         <v>0.3978343952398426</v>
       </c>
     </row>
-    <row r="186" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>24</v>
@@ -12204,7 +12187,7 @@
         <v>25</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F186" s="5">
         <v>1</v>
@@ -12250,12 +12233,12 @@
         <v>0.17269476854625965</v>
       </c>
     </row>
-    <row r="187" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>24</v>
@@ -12264,7 +12247,7 @@
         <v>25</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F187" s="5">
         <v>2</v>
@@ -12310,12 +12293,12 @@
         <v>0.19835783930756376</v>
       </c>
     </row>
-    <row r="188" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>24</v>
@@ -12324,7 +12307,7 @@
         <v>25</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F188" s="5">
         <v>3</v>
@@ -12370,12 +12353,12 @@
         <v>0.19167300936492349</v>
       </c>
     </row>
-    <row r="189" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>24</v>
@@ -12384,7 +12367,7 @@
         <v>25</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F189" s="5">
         <v>4</v>
@@ -12430,12 +12413,12 @@
         <v>0.18075040551918067</v>
       </c>
     </row>
-    <row r="190" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>24</v>
@@ -12444,7 +12427,7 @@
         <v>25</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F190" s="5">
         <v>5</v>
@@ -12490,12 +12473,12 @@
         <v>0.16694755264545161</v>
       </c>
     </row>
-    <row r="191" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>24</v>
@@ -12504,7 +12487,7 @@
         <v>25</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F191" s="5">
         <v>6</v>
@@ -12550,21 +12533,21 @@
         <v>0.17269476854625965</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F192" s="5">
         <v>1</v>
@@ -12610,21 +12593,21 @@
         <v>0.227950665561552</v>
       </c>
     </row>
-    <row r="193" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F193" s="5">
         <v>3</v>
@@ -12670,21 +12653,21 @@
         <v>0.20169846999357632</v>
       </c>
     </row>
-    <row r="194" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F194" s="5">
         <v>4</v>
@@ -12730,21 +12713,21 @@
         <v>0.18779561009166973</v>
       </c>
     </row>
-    <row r="195" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F195" s="5">
         <v>5</v>
@@ -12790,21 +12773,21 @@
         <v>0.18128750429909135</v>
       </c>
     </row>
-    <row r="196" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C196" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F196" s="5">
         <v>6</v>
@@ -12850,12 +12833,12 @@
         <v>0.12862110976115759</v>
       </c>
     </row>
-    <row r="197" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>29</v>
@@ -12864,10 +12847,10 @@
         <v>37</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G197" s="5" t="str">
         <f t="shared" si="5"/>
@@ -12910,12 +12893,12 @@
         <v>0.30767742800929487</v>
       </c>
     </row>
-    <row r="198" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>29</v>
@@ -12924,10 +12907,10 @@
         <v>37</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G198" s="5" t="str">
         <f t="shared" si="5"/>
@@ -12970,12 +12953,12 @@
         <v>0.21562634827428284</v>
       </c>
     </row>
-    <row r="199" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>29</v>
@@ -12984,10 +12967,10 @@
         <v>37</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G199" s="5" t="str">
         <f t="shared" si="5"/>
@@ -13030,12 +13013,12 @@
         <v>0.21562634827428284</v>
       </c>
     </row>
-    <row r="200" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>29</v>
@@ -13044,10 +13027,10 @@
         <v>37</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G200" s="5" t="str">
         <f t="shared" si="5"/>
@@ -13090,12 +13073,12 @@
         <v>0.18737393878469991</v>
       </c>
     </row>
-    <row r="201" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C201" s="5" t="s">
         <v>29</v>
@@ -13104,10 +13087,10 @@
         <v>37</v>
       </c>
       <c r="E201" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F201" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="G201" s="5" t="str">
         <f t="shared" si="5"/>
@@ -13150,12 +13133,12 @@
         <v>0.19871518091456961</v>
       </c>
     </row>
-    <row r="202" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>29</v>
@@ -13164,7 +13147,7 @@
         <v>25</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F202" s="5">
         <v>1</v>
@@ -13210,12 +13193,12 @@
         <v>0.15395820386458711</v>
       </c>
     </row>
-    <row r="203" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>29</v>
@@ -13224,7 +13207,7 @@
         <v>25</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F203" s="5">
         <v>2</v>
@@ -13270,12 +13253,12 @@
         <v>0.1495389567337079</v>
       </c>
     </row>
-    <row r="204" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>29</v>
@@ -13284,7 +13267,7 @@
         <v>25</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F204" s="5">
         <v>3</v>
@@ -13330,12 +13313,12 @@
         <v>0.13516431886169203</v>
       </c>
     </row>
-    <row r="205" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>29</v>
@@ -13344,7 +13327,7 @@
         <v>25</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F205" s="5">
         <v>4</v>
@@ -13390,12 +13373,12 @@
         <v>8.8955129848971207E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>29</v>
@@ -13404,7 +13387,7 @@
         <v>25</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F206" s="5">
         <v>5</v>
@@ -13450,12 +13433,12 @@
         <v>0.14822817697262225</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>29</v>
@@ -13464,7 +13447,7 @@
         <v>25</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F207" s="5">
         <v>6</v>
@@ -13510,21 +13493,21 @@
         <v>0.16501379728804133</v>
       </c>
     </row>
-    <row r="208" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F208" s="5">
         <v>1</v>
@@ -13570,21 +13553,21 @@
         <v>0.19493344739157487</v>
       </c>
     </row>
-    <row r="209" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F209" s="5">
         <v>2</v>
@@ -13630,21 +13613,21 @@
         <v>0.18193425570084554</v>
       </c>
     </row>
-    <row r="210" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F210" s="5">
         <v>3</v>
@@ -13690,21 +13673,21 @@
         <v>0.13184939118166397</v>
       </c>
     </row>
-    <row r="211" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F211" s="5">
         <v>4</v>
@@ -13750,21 +13733,21 @@
         <v>0.22481937717233275</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F212" s="5">
         <v>5</v>
@@ -13810,21 +13793,21 @@
         <v>0.1041258247703592</v>
       </c>
     </row>
-    <row r="213" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F213" s="5">
         <v>1</v>
@@ -13870,21 +13853,21 @@
         <v>9.9154090187250452E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F214" s="5">
         <v>2</v>
@@ -13930,21 +13913,21 @@
         <v>8.1244772710969249E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F215" s="5">
         <v>4</v>
@@ -13990,21 +13973,21 @@
         <v>9.3020519030123344E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C216" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F216" s="5">
         <v>5</v>
@@ -14050,21 +14033,21 @@
         <v>0.16055724188527687</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F217" s="5">
         <v>6</v>
@@ -14110,12 +14093,12 @@
         <v>6.7039140566223107E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>29</v>
@@ -14124,7 +14107,7 @@
         <v>25</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F218" s="5">
         <v>1</v>
@@ -14170,12 +14153,12 @@
         <v>0.18847166401362775</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C219" s="5" t="s">
         <v>29</v>
@@ -14184,7 +14167,7 @@
         <v>25</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F219" s="5">
         <v>2</v>
@@ -14230,12 +14213,12 @@
         <v>0.20339468518193859</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C220" s="5" t="s">
         <v>29</v>
@@ -14244,7 +14227,7 @@
         <v>25</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F220" s="5">
         <v>3</v>
@@ -14290,12 +14273,12 @@
         <v>0.2134068947259225</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>29</v>
@@ -14304,7 +14287,7 @@
         <v>25</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F221" s="5">
         <v>4</v>
@@ -14350,12 +14333,12 @@
         <v>0.17582102133218075</v>
       </c>
     </row>
-    <row r="222" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C222" s="5" t="s">
         <v>29</v>
@@ -14364,7 +14347,7 @@
         <v>25</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F222" s="5">
         <v>5</v>
@@ -14410,12 +14393,12 @@
         <v>0.19566540303506627</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C223" s="5" t="s">
         <v>29</v>
@@ -14424,7 +14407,7 @@
         <v>25</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F223" s="5">
         <v>6</v>
@@ -14470,12 +14453,12 @@
         <v>0.18390218310174256</v>
       </c>
     </row>
-    <row r="224" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>29</v>
@@ -14484,7 +14467,7 @@
         <v>25</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F224" s="5">
         <v>1</v>
@@ -14530,12 +14513,12 @@
         <v>0.21238579552650738</v>
       </c>
     </row>
-    <row r="225" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C225" s="5" t="s">
         <v>29</v>
@@ -14544,7 +14527,7 @@
         <v>25</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F225" s="5">
         <v>2</v>
@@ -14590,12 +14573,12 @@
         <v>0.25609861217140883</v>
       </c>
     </row>
-    <row r="226" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C226" s="5" t="s">
         <v>29</v>
@@ -14604,7 +14587,7 @@
         <v>25</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F226" s="5">
         <v>3</v>
@@ -14650,12 +14633,12 @@
         <v>0.26977278174207148</v>
       </c>
     </row>
-    <row r="227" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>29</v>
@@ -14664,7 +14647,7 @@
         <v>25</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F227" s="5">
         <v>4</v>
@@ -14710,12 +14693,12 @@
         <v>0.23161724099804892</v>
       </c>
     </row>
-    <row r="228" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C228" s="5" t="s">
         <v>29</v>
@@ -14724,7 +14707,7 @@
         <v>25</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F228" s="5">
         <v>5</v>
@@ -14770,12 +14753,12 @@
         <v>0.23204639194451276</v>
       </c>
     </row>
-    <row r="229" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>29</v>
@@ -14784,7 +14767,7 @@
         <v>25</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F229" s="5">
         <v>6</v>
@@ -14830,21 +14813,21 @@
         <v>0.23682871174934256</v>
       </c>
     </row>
-    <row r="230" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F230" s="5">
         <v>1</v>
@@ -14890,21 +14873,21 @@
         <v>0.15509723484088975</v>
       </c>
     </row>
-    <row r="231" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C231" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F231" s="5">
         <v>2</v>
@@ -14950,21 +14933,21 @@
         <v>0.14769988613579188</v>
       </c>
     </row>
-    <row r="232" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C232" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F232" s="5">
         <v>3</v>
@@ -15010,21 +14993,21 @@
         <v>0.15333538473877517</v>
       </c>
     </row>
-    <row r="233" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C233" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F233" s="5">
         <v>4</v>
@@ -15070,21 +15053,21 @@
         <v>0.23900118335181761</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C234" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F234" s="5">
         <v>5</v>
@@ -15130,21 +15113,21 @@
         <v>0.13238979085034711</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F235" s="5">
         <v>1</v>
@@ -15190,21 +15173,21 @@
         <v>0.35374914571111715</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C236" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F236" s="5">
         <v>2</v>
@@ -15250,21 +15233,21 @@
         <v>0.21150838968879188</v>
       </c>
     </row>
-    <row r="237" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F237" s="5">
         <v>4</v>
@@ -15310,21 +15293,21 @@
         <v>0.33755912369988406</v>
       </c>
     </row>
-    <row r="238" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C238" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F238" s="5">
         <v>5</v>
@@ -15370,21 +15353,21 @@
         <v>0.31665778879234385</v>
       </c>
     </row>
-    <row r="239" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C239" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F239" s="5">
         <v>6</v>
@@ -15430,12 +15413,12 @@
         <v>0.37803089926640004</v>
       </c>
     </row>
-    <row r="240" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C240" s="5" t="s">
         <v>29</v>
@@ -15444,7 +15427,7 @@
         <v>25</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F240" s="5">
         <v>1</v>
@@ -15490,12 +15473,12 @@
         <v>0.26519303848678932</v>
       </c>
     </row>
-    <row r="241" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C241" s="5" t="s">
         <v>29</v>
@@ -15504,7 +15487,7 @@
         <v>25</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F241" s="5">
         <v>2</v>
@@ -15550,12 +15533,12 @@
         <v>0.31598168913507119</v>
       </c>
     </row>
-    <row r="242" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C242" s="5" t="s">
         <v>29</v>
@@ -15564,7 +15547,7 @@
         <v>25</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F242" s="5">
         <v>3</v>
@@ -15610,12 +15593,12 @@
         <v>0.33374872776994247</v>
       </c>
     </row>
-    <row r="243" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C243" s="5" t="s">
         <v>29</v>
@@ -15624,7 +15607,7 @@
         <v>25</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F243" s="5">
         <v>4</v>
@@ -15670,12 +15653,12 @@
         <v>0.28272233449809242</v>
       </c>
     </row>
-    <row r="244" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C244" s="5" t="s">
         <v>29</v>
@@ -15684,7 +15667,7 @@
         <v>25</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F244" s="5">
         <v>5</v>
@@ -15730,12 +15713,12 @@
         <v>0.26013225400440704</v>
       </c>
     </row>
-    <row r="245" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C245" s="5" t="s">
         <v>29</v>
@@ -15744,7 +15727,7 @@
         <v>25</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F245" s="5">
         <v>6</v>
@@ -15790,21 +15773,21 @@
         <v>0.29319676507830161</v>
       </c>
     </row>
-    <row r="246" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C246" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F246" s="5">
         <v>1</v>
@@ -15850,21 +15833,21 @@
         <v>0.61619000844737215</v>
       </c>
     </row>
-    <row r="247" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C247" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F247" s="5">
         <v>2</v>
@@ -15910,21 +15893,21 @@
         <v>0.55160860552664581</v>
       </c>
     </row>
-    <row r="248" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C248" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F248" s="5">
         <v>3</v>
@@ -15970,21 +15953,21 @@
         <v>0.51033544015235255</v>
       </c>
     </row>
-    <row r="249" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C249" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F249" s="5">
         <v>4</v>
@@ -16030,21 +16013,21 @@
         <v>0.61489019348324581</v>
       </c>
     </row>
-    <row r="250" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C250" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F250" s="5">
         <v>5</v>
@@ -16090,21 +16073,21 @@
         <v>0.59271870479657618</v>
       </c>
     </row>
-    <row r="251" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C251" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F251" s="5">
         <v>6</v>
@@ -16150,21 +16133,21 @@
         <v>0.50649577363860243</v>
       </c>
     </row>
-    <row r="252" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C252" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F252" s="5">
         <v>1</v>
@@ -16210,21 +16193,21 @@
         <v>0.40701045217151488</v>
       </c>
     </row>
-    <row r="253" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C253" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F253" s="5">
         <v>2</v>
@@ -16270,21 +16253,21 @@
         <v>0.38785155678403405</v>
       </c>
     </row>
-    <row r="254" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C254" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F254" s="5">
         <v>3</v>
@@ -16330,21 +16313,21 @@
         <v>0.4780143316769962</v>
       </c>
     </row>
-    <row r="255" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C255" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F255" s="5">
         <v>4</v>
@@ -16390,21 +16373,21 @@
         <v>0.51913877392244001</v>
       </c>
     </row>
-    <row r="256" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C256" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F256" s="5">
         <v>5</v>
@@ -16450,21 +16433,21 @@
         <v>0.45224668967210402</v>
       </c>
     </row>
-    <row r="257" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F257" s="5">
         <v>6</v>
@@ -16510,21 +16493,21 @@
         <v>0.42731212374971167</v>
       </c>
     </row>
-    <row r="258" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C258" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F258" s="5">
         <v>1</v>
@@ -16570,21 +16553,21 @@
         <v>0.30524813096342679</v>
       </c>
     </row>
-    <row r="259" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F259" s="5">
         <v>2</v>
@@ -16630,21 +16613,21 @@
         <v>0.24042793960079001</v>
       </c>
     </row>
-    <row r="260" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F260" s="5">
         <v>3</v>
@@ -16690,21 +16673,21 @@
         <v>0.26335101013496998</v>
       </c>
     </row>
-    <row r="261" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F261" s="5">
         <v>4</v>
@@ -16750,21 +16733,21 @@
         <v>0.26439472934839836</v>
       </c>
     </row>
-    <row r="262" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C262" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F262" s="5">
         <v>5</v>
@@ -16810,21 +16793,21 @@
         <v>0.2778073654482443</v>
       </c>
     </row>
-    <row r="263" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C263" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F263" s="5">
         <v>6</v>
@@ -16870,21 +16853,21 @@
         <v>0.3071416256329515</v>
       </c>
     </row>
-    <row r="264" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C264" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F264" s="5">
         <v>1</v>
@@ -16930,21 +16913,21 @@
         <v>0.62062518891831608</v>
       </c>
     </row>
-    <row r="265" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F265" s="5">
         <v>2</v>
@@ -16990,21 +16973,21 @@
         <v>0.62262457998062681</v>
       </c>
     </row>
-    <row r="266" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C266" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F266" s="5">
         <v>3</v>
@@ -17050,21 +17033,21 @@
         <v>0.5304844410526719</v>
       </c>
     </row>
-    <row r="267" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F267" s="5">
         <v>5</v>
@@ -17110,21 +17093,21 @@
         <v>0.5853492146880922</v>
       </c>
     </row>
-    <row r="268" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C268" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F268" s="5">
         <v>6</v>
@@ -17170,9 +17153,9 @@
         <v>0.65312501668118594</v>
       </c>
     </row>
-    <row r="269" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B269" s="8" t="s">
         <v>28</v>
@@ -17184,7 +17167,7 @@
         <v>37</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F269" s="8">
         <v>604071</v>
@@ -17230,9 +17213,9 @@
       </c>
       <c r="S269" s="9"/>
     </row>
-    <row r="270" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B270" s="8" t="s">
         <v>28</v>
@@ -17244,7 +17227,7 @@
         <v>37</v>
       </c>
       <c r="E270" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F270" s="8">
         <v>1409175</v>
@@ -17290,9 +17273,9 @@
       </c>
       <c r="S270" s="9"/>
     </row>
-    <row r="271" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B271" s="8" t="s">
         <v>28</v>
@@ -17304,7 +17287,7 @@
         <v>37</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F271" s="8">
         <v>1509057</v>
@@ -17350,9 +17333,9 @@
       </c>
       <c r="S271" s="9"/>
     </row>
-    <row r="272" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B272" s="8" t="s">
         <v>28</v>
@@ -17364,7 +17347,7 @@
         <v>37</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F272" s="8">
         <v>1509076</v>
@@ -17410,9 +17393,9 @@
       </c>
       <c r="S272" s="9"/>
     </row>
-    <row r="273" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B273" s="8" t="s">
         <v>28</v>
@@ -17424,7 +17407,7 @@
         <v>37</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F273" s="8">
         <v>1509082</v>
@@ -17470,12 +17453,12 @@
       </c>
       <c r="S273" s="9"/>
     </row>
-    <row r="274" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>29</v>
@@ -17484,7 +17467,7 @@
         <v>37</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F274" s="8">
         <v>408117</v>
@@ -17530,12 +17513,12 @@
       </c>
       <c r="S274" s="9"/>
     </row>
-    <row r="275" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>29</v>
@@ -17544,7 +17527,7 @@
         <v>37</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F275" s="8">
         <v>617094</v>
@@ -17590,12 +17573,12 @@
       </c>
       <c r="S275" s="9"/>
     </row>
-    <row r="276" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C276" s="8" t="s">
         <v>29</v>
@@ -17604,7 +17587,7 @@
         <v>37</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F276" s="8">
         <v>719191</v>
@@ -17650,12 +17633,12 @@
       </c>
       <c r="S276" s="9"/>
     </row>
-    <row r="277" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>29</v>
@@ -17664,7 +17647,7 @@
         <v>37</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F277" s="8">
         <v>920024</v>
@@ -17710,12 +17693,12 @@
       </c>
       <c r="S277" s="9"/>
     </row>
-    <row r="278" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>29</v>
@@ -17724,7 +17707,7 @@
         <v>37</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F278" s="8">
         <v>1020023</v>
@@ -17770,12 +17753,12 @@
       </c>
       <c r="S278" s="9"/>
     </row>
-    <row r="279" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>29</v>
@@ -17784,7 +17767,7 @@
         <v>37</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F279" s="8">
         <v>1511057</v>
@@ -17830,12 +17813,12 @@
       </c>
       <c r="S279" s="9"/>
     </row>
-    <row r="280" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>29</v>
@@ -17844,7 +17827,7 @@
         <v>25</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F280" s="5">
         <v>1</v>
@@ -17890,12 +17873,12 @@
         <v>0.25340302964120975</v>
       </c>
     </row>
-    <row r="281" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>29</v>
@@ -17904,7 +17887,7 @@
         <v>25</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F281" s="5">
         <v>2</v>
@@ -17950,12 +17933,12 @@
         <v>0.1467619756941089</v>
       </c>
     </row>
-    <row r="282" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>29</v>
@@ -17964,7 +17947,7 @@
         <v>25</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F282" s="5">
         <v>3</v>
@@ -18010,12 +17993,12 @@
         <v>0.24834621661679035</v>
       </c>
     </row>
-    <row r="283" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C283" s="5" t="s">
         <v>29</v>
@@ -18024,7 +18007,7 @@
         <v>25</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F283" s="5">
         <v>4</v>
@@ -18070,12 +18053,12 @@
         <v>0.22486989894233841</v>
       </c>
     </row>
-    <row r="284" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C284" s="5" t="s">
         <v>29</v>
@@ -18084,7 +18067,7 @@
         <v>25</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F284" s="5">
         <v>5</v>
@@ -18130,12 +18113,12 @@
         <v>0.21226643700457165</v>
       </c>
     </row>
-    <row r="285" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C285" s="5" t="s">
         <v>29</v>
@@ -18144,7 +18127,7 @@
         <v>25</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F285" s="5">
         <v>6</v>
@@ -18190,12 +18173,12 @@
         <v>0.19664510614270117</v>
       </c>
     </row>
-    <row r="286" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C286" s="5" t="s">
         <v>24</v>
@@ -18204,7 +18187,7 @@
         <v>25</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F286" s="5">
         <v>2</v>
@@ -18250,12 +18233,12 @@
         <v>0.52632024643914144</v>
       </c>
     </row>
-    <row r="287" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>24</v>
@@ -18264,7 +18247,7 @@
         <v>25</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F287" s="5">
         <v>3</v>
@@ -18310,12 +18293,12 @@
         <v>0.46249209574305439</v>
       </c>
     </row>
-    <row r="288" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C288" s="5" t="s">
         <v>24</v>
@@ -18324,7 +18307,7 @@
         <v>25</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F288" s="5">
         <v>4</v>
@@ -18370,12 +18353,12 @@
         <v>0.43554821232641577</v>
       </c>
     </row>
-    <row r="289" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C289" s="5" t="s">
         <v>24</v>
@@ -18384,7 +18367,7 @@
         <v>25</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F289" s="5">
         <v>5</v>
@@ -18430,12 +18413,12 @@
         <v>0.5189802724722089</v>
       </c>
     </row>
-    <row r="290" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C290" s="5" t="s">
         <v>24</v>
@@ -18444,7 +18427,7 @@
         <v>25</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F290" s="5">
         <v>6</v>
@@ -18490,12 +18473,12 @@
         <v>0.36155761293341565</v>
       </c>
     </row>
-    <row r="291" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>24</v>
@@ -18504,7 +18487,7 @@
         <v>25</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F291" s="5">
         <v>1</v>
@@ -18550,12 +18533,12 @@
         <v>0.45375755505261417</v>
       </c>
     </row>
-    <row r="292" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C292" s="5" t="s">
         <v>24</v>
@@ -18564,7 +18547,7 @@
         <v>25</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F292" s="5">
         <v>2</v>
@@ -18610,12 +18593,12 @@
         <v>0.33783554955494999</v>
       </c>
     </row>
-    <row r="293" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C293" s="5" t="s">
         <v>24</v>
@@ -18624,7 +18607,7 @@
         <v>25</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F293" s="5">
         <v>3</v>
@@ -18670,12 +18653,12 @@
         <v>0.31502943165482172</v>
       </c>
     </row>
-    <row r="294" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C294" s="5" t="s">
         <v>24</v>
@@ -18684,7 +18667,7 @@
         <v>25</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F294" s="5">
         <v>4</v>
@@ -18730,12 +18713,12 @@
         <v>0.40672751744998198</v>
       </c>
     </row>
-    <row r="295" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C295" s="5" t="s">
         <v>24</v>
@@ -18744,7 +18727,7 @@
         <v>25</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F295" s="5">
         <v>5</v>
